--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N25_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>19.64932736938029</v>
       </c>
       <c r="E2" t="n">
-        <v>15.99274821622051</v>
+        <v>18.04585613841753</v>
       </c>
       <c r="F2" t="n">
-        <v>18.12703662631974</v>
+        <v>19.30183189428035</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>9.466350084866805</v>
       </c>
       <c r="E3" t="n">
-        <v>15.99274821622051</v>
+        <v>18.04585613841753</v>
       </c>
       <c r="F3" t="n">
-        <v>18.12703662631974</v>
+        <v>19.30183189428035</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>17.27995980302856</v>
       </c>
       <c r="E4" t="n">
-        <v>15.99274821622051</v>
+        <v>18.04585613841753</v>
       </c>
       <c r="F4" t="n">
-        <v>18.12703662631974</v>
+        <v>19.30183189428035</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>33.20494071871703</v>
       </c>
       <c r="E5" t="n">
-        <v>15.99274821622051</v>
+        <v>18.04585613841753</v>
       </c>
       <c r="F5" t="n">
-        <v>18.12703662631974</v>
+        <v>19.30183189428035</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.6136746960658</v>
+        <v>2.359520157067053</v>
       </c>
       <c r="D6" t="n">
-        <v>27.54040537372187</v>
+        <v>1.555905135486368</v>
       </c>
       <c r="E6" t="n">
-        <v>15.99274821622051</v>
+        <v>18.04585613841753</v>
       </c>
       <c r="F6" t="n">
-        <v>18.12703662631974</v>
+        <v>19.30183189428035</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,23 +640,55 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
+        <v>27.6136746960658</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27.54040537372187</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18.04585613841753</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19.30183189428035</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W0065F0002T0006Z000C1N25.png</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
         <v>65.60511017316423</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>65.68238869734743</v>
       </c>
-      <c r="E7" t="n">
-        <v>15.99274821622051</v>
-      </c>
-      <c r="F7" t="n">
-        <v>18.12703662631974</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E8" t="n">
+        <v>18.04585613841753</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.30183189428035</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>T12594</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.41824645358994</v>
+        <v>3.155465048708365</v>
       </c>
       <c r="D2" t="n">
-        <v>19.64932736938029</v>
+        <v>3.193015697524298</v>
       </c>
       <c r="E2" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F2" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.42333056454669</v>
+        <v>4.456291216738837</v>
       </c>
       <c r="D3" t="n">
-        <v>9.466350084866805</v>
+        <v>1.538281888790856</v>
       </c>
       <c r="E3" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F3" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.67317900134893</v>
+        <v>2.871891587719202</v>
       </c>
       <c r="D4" t="n">
-        <v>17.27995980302856</v>
+        <v>2.807993467992142</v>
       </c>
       <c r="E4" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F4" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.30892348286085</v>
+        <v>5.412700065964888</v>
       </c>
       <c r="D5" t="n">
-        <v>33.20494071871703</v>
+        <v>5.395802866791517</v>
       </c>
       <c r="E5" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F5" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.359520157067053</v>
+        <v>0.383422025523396</v>
       </c>
       <c r="D6" t="n">
-        <v>1.555905135486368</v>
+        <v>0.2528345845165349</v>
       </c>
       <c r="E6" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F6" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.6136746960658</v>
+        <v>4.487222138110693</v>
       </c>
       <c r="D7" t="n">
-        <v>27.54040537372187</v>
+        <v>4.475315873229805</v>
       </c>
       <c r="E7" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F7" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.60511017316423</v>
+        <v>10.66083040313919</v>
       </c>
       <c r="D8" t="n">
-        <v>65.68238869734743</v>
+        <v>10.67338816331896</v>
       </c>
       <c r="E8" t="n">
-        <v>18.04585613841753</v>
+        <v>2.932451622492849</v>
       </c>
       <c r="F8" t="n">
-        <v>19.30183189428035</v>
+        <v>3.136547682820557</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
